--- a/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -575,13 +575,15 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
-      <x:c r="A13" s="0">
+      <x:c r="A13" s="0" t="str">
         <x:f>SUM(8:9)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
-      <x:c r="A14" s="0">
+      <x:c r="A14" s="0" t="str">
         <x:f>SUM(8:9)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -556,6 +556,12 @@
         <x:f t="array" ref="B6:B6">A2+A3</x:f>
         <x:v>2</x:v>
       </x:c>
+      <x:c r="C6" s="0">
+        <x:f t="array" ref="C6:D6">TRANSPOSE(A2:A3)</x:f>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:f t="array"/>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="n">

--- a/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -103,7 +103,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF00FFFF"/>
-        <x:bgColor rgb="FF00FFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>

--- a/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/ClosedXML_Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -479,7 +479,7 @@
       <x:c r="B2" s="0" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="str">
+      <x:c r="C2" s="0" t="n">
         <x:f>A2+$B$2</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -504,7 +504,7 @@
       <x:c r="B3" s="0" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="str">
+      <x:c r="C3" s="0" t="n">
         <x:f>A3+$B$3</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -551,7 +551,7 @@
       <x:c r="A6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="str">
+      <x:c r="B6" s="0" t="n">
         <x:f t="array" ref="B6:B6">A2+A3</x:f>
         <x:v>2</x:v>
       </x:c>
@@ -568,25 +568,25 @@
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
-      <x:c r="A11" s="0" t="str">
+      <x:c r="A11" s="0" t="n">
         <x:f>A2 + A10_R1C1_A10_R1C1</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
-      <x:c r="A12" s="0" t="str">
+      <x:c r="A12" s="0" t="n">
         <x:f>$A$2 + A10_R1C1_A10_R1C1</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
-      <x:c r="A13" s="0" t="str">
+      <x:c r="A13" s="0" t="n">
         <x:f>SUM(8:9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
-      <x:c r="A14" s="0" t="str">
+      <x:c r="A14" s="0" t="n">
         <x:f>SUM(8:9)</x:f>
         <x:v>0</x:v>
       </x:c>
